--- a/artfynd/A 60260-2025 artfynd.xlsx
+++ b/artfynd/A 60260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113511114</v>
+        <v>113508001</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552664</v>
+        <v>552517</v>
       </c>
       <c r="R2" t="n">
-        <v>7037824</v>
+        <v>7037817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113508001</v>
+        <v>113511113</v>
       </c>
       <c r="B3" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552517</v>
+        <v>552647</v>
       </c>
       <c r="R3" t="n">
-        <v>7037817</v>
+        <v>7037857</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -876,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511115</v>
+        <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552665</v>
+        <v>552431</v>
       </c>
       <c r="R4" t="n">
-        <v>7037814</v>
+        <v>7037803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511113</v>
+        <v>113511111</v>
       </c>
       <c r="B5" t="n">
-        <v>79427</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>385</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552647</v>
+        <v>552769</v>
       </c>
       <c r="R5" t="n">
-        <v>7037857</v>
+        <v>7037841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,6 +1073,521 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113511114</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552664</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037824</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113511110</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113511107</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552751</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113511108</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552752</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037884</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113511115</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552665</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037814</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 60260-2025 artfynd.xlsx
+++ b/artfynd/A 60260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113508001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511113</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511114</t>
         </is>
       </c>
     </row>
@@ -1289,6 +1319,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511110</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511107</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511108</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,8 +1637,24 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113511115</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>